--- a/Server/NewServer/bin/commonconfig/setting/pet.xlsx
+++ b/Server/NewServer/bin/commonconfig/setting/pet.xlsx
@@ -32,7 +32,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -43,7 +43,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-取值范围</t>
+Allowed range</t>
         </r>
         <r>
           <rPr>
@@ -67,7 +67,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>作者:</t>
+          <t>Author:</t>
         </r>
         <r>
           <rPr>
@@ -78,7 +78,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-取值范围</t>
+Allowed range</t>
         </r>
         <r>
           <rPr>
